--- a/output_results.xlsx
+++ b/output_results.xlsx
@@ -62,8 +62,8 @@
  [158 895]]</t>
   </si>
   <si>
-    <t>[[658 193]
- [150 903]]</t>
+    <t>[[662 189]
+ [141 912]]</t>
   </si>
   <si>
     <t>[[697 154]
@@ -94,7 +94,7 @@
  [ 28  69]]</t>
   </si>
   <si>
-    <t>[[94 19]
+    <t>[[92 21]
  [23 74]]</t>
   </si>
   <si>
@@ -126,7 +126,7 @@
  [ 0 58]]</t>
   </si>
   <si>
-    <t>[[13  7]
+    <t>[[14  6]
  [ 6 52]]</t>
   </si>
   <si>
@@ -159,7 +159,7 @@
   </si>
   <si>
     <t>[[14  6]
- [ 6 64]]</t>
+ [ 4 66]]</t>
   </si>
   <si>
     <t>[[13  7]
@@ -190,8 +190,8 @@
  [184 912]]</t>
   </si>
   <si>
-    <t>[[675 194]
- [170 926]]</t>
+    <t>[[668 201]
+ [203 893]]</t>
   </si>
   <si>
     <t>[[641 228]
@@ -223,7 +223,7 @@
   </si>
   <si>
     <t>[[763 221]
- [328 880]]</t>
+ [375 833]]</t>
   </si>
   <si>
     <t>[[796 188]
@@ -254,8 +254,8 @@
  [112 156]]</t>
   </si>
   <si>
-    <t>[[125  48]
- [ 85 183]]</t>
+    <t>[[124  49]
+ [ 90 178]]</t>
   </si>
   <si>
     <t>[[ 95  78]
@@ -286,8 +286,8 @@
  [400 921]]</t>
   </si>
   <si>
-    <t>[[778 246]
- [355 966]]</t>
+    <t>[[799 225]
+ [338 983]]</t>
   </si>
   <si>
     <t>[[705 319]
@@ -317,7 +317,7 @@
     <t>{'Flaky': {'precision': 0.8158508158508159, 'recall': 0.8225616921269095, 'f1-score': 0.8191925102399065, 'support': 851.0}, 'NonFlaky': {'precision': 0.8556405353728489, 'recall': 0.8499525166191833, 'f1-score': 0.8527870414483087, 'support': 1053.0}, 'accuracy': 0.8377100840336135, 'macro avg': {'precision': 0.8357456756118324, 'recall': 0.8362571043730465, 'f1-score': 0.8359897758441076, 'support': 1904.0}, 'weighted avg': {'precision': 0.8378563697671504, 'recall': 0.8377100840336135, 'f1-score': 0.8377718386865701, 'support': 1904.0}}</t>
   </si>
   <si>
-    <t>{'Flaky': {'precision': 0.8143564356435643, 'recall': 0.7732079905992949, 'f1-score': 0.7932489451476793, 'support': 851.0}, 'NonFlaky': {'precision': 0.823905109489051, 'recall': 0.8575498575498576, 'f1-score': 0.8403908794788274, 'support': 1053.0}, 'accuracy': 0.8198529411764706, 'macro avg': {'precision': 0.8191307725663077, 'recall': 0.8153789240745762, 'f1-score': 0.8168199123132533, 'support': 1904.0}, 'weighted avg': {'precision': 0.8196372936053803, 'recall': 0.8198529411764706, 'f1-score': 0.8193206136617018, 'support': 1904.0}}</t>
+    <t>{'Flaky': {'precision': 0.8244084682440846, 'recall': 0.7779083431257344, 'f1-score': 0.8004836759371221, 'support': 851.0}, 'NonFlaky': {'precision': 0.8283378746594006, 'recall': 0.8660968660968661, 'f1-score': 0.8467966573816155, 'support': 1053.0}, 'accuracy': 0.8266806722689075, 'macro avg': {'precision': 0.8263731714517426, 'recall': 0.8220026046113003, 'f1-score': 0.8236401666593688, 'support': 1904.0}, 'weighted avg': {'precision': 0.8265816116029753, 'recall': 0.8266806722689075, 'f1-score': 0.826096895191876, 'support': 1904.0}}</t>
   </si>
   <si>
     <t>{'Flaky': {'precision': 0.7215320910973085, 'recall': 0.8190364277320799, 'f1-score': 0.767198679141442, 'support': 851.0}, 'NonFlaky': {'precision': 0.835820895522388, 'recall': 0.7445394112060779, 'f1-score': 0.7875439477649423, 'support': 1053.0}, 'accuracy': 0.7778361344537815, 'macro avg': {'precision': 0.7786764933098482, 'recall': 0.7817879194690789, 'f1-score': 0.7773713134531921, 'support': 1904.0}, 'weighted avg': {'precision': 0.7847390822000442, 'recall': 0.7778361344537815, 'f1-score': 0.778450553017779, 'support': 1904.0}}</t>
@@ -341,7 +341,7 @@
     <t>{'Flaky': {'precision': 0.8, 'recall': 0.9911504424778761, 'f1-score': 0.8853754940711462, 'support': 113.0}, 'NonFlaky': {'precision': 0.9857142857142858, 'recall': 0.711340206185567, 'f1-score': 0.8263473053892215, 'support': 97.0}, 'accuracy': 0.861904761904762, 'macro avg': {'precision': 0.8928571428571429, 'recall': 0.8512453243317215, 'f1-score': 0.8558613997301838, 'support': 210.0}, 'weighted avg': {'precision': 0.8857823129251702, 'recall': 0.861904761904762, 'f1-score': 0.8581100926323524, 'support': 210.0}}</t>
   </si>
   <si>
-    <t>{'Flaky': {'precision': 0.8034188034188035, 'recall': 0.831858407079646, 'f1-score': 0.817391304347826, 'support': 113.0}, 'NonFlaky': {'precision': 0.7956989247311828, 'recall': 0.7628865979381443, 'f1-score': 0.7789473684210526, 'support': 97.0}, 'accuracy': 0.8, 'macro avg': {'precision': 0.7995588640749931, 'recall': 0.7973725025088951, 'f1-score': 0.7981693363844393, 'support': 210.0}, 'weighted avg': {'precision': 0.7998529546916643, 'recall': 0.8, 'f1-score': 0.7996338672768878, 'support': 210.0}}</t>
+    <t>{'Flaky': {'precision': 0.8, 'recall': 0.8141592920353983, 'f1-score': 0.8070175438596492, 'support': 113.0}, 'NonFlaky': {'precision': 0.7789473684210526, 'recall': 0.7628865979381443, 'f1-score': 0.7708333333333333, 'support': 97.0}, 'accuracy': 0.7904761904761904, 'macro avg': {'precision': 0.7894736842105263, 'recall': 0.7885229449867712, 'f1-score': 0.7889254385964912, 'support': 210.0}, 'weighted avg': {'precision': 0.7902756892230576, 'recall': 0.7904761904761904, 'f1-score': 0.7903038847117795, 'support': 210.0}}</t>
   </si>
   <si>
     <t>{'Flaky': {'precision': 0.84375, 'recall': 0.7168141592920354, 'f1-score': 0.7751196172248803, 'support': 113.0}, 'NonFlaky': {'precision': 0.7192982456140351, 'recall': 0.845360824742268, 'f1-score': 0.7772511848341231, 'support': 97.0}, 'accuracy': 0.7761904761904762, 'macro avg': {'precision': 0.7815241228070176, 'recall': 0.7810874920171518, 'f1-score': 0.7761854010295017, 'support': 210.0}, 'weighted avg': {'precision': 0.786265142021721, 'recall': 0.7761904761904762, 'f1-score': 0.7761041984539114, 'support': 210.0}}</t>
@@ -365,7 +365,7 @@
     <t>{'Flaky': {'precision': 1.0, 'recall': 0.8, 'f1-score': 0.888888888888889, 'support': 20.0}, 'NonFlaky': {'precision': 0.9354838709677419, 'recall': 1.0, 'f1-score': 0.9666666666666666, 'support': 58.0}, 'accuracy': 0.9487179487179487, 'macro avg': {'precision': 0.967741935483871, 'recall': 0.9, 'f1-score': 0.9277777777777778, 'support': 78.0}, 'weighted avg': {'precision': 0.9520264681555003, 'recall': 0.9487179487179487, 'f1-score': 0.9467236467236466, 'support': 78.0}}</t>
   </si>
   <si>
-    <t>{'Flaky': {'precision': 0.6842105263157895, 'recall': 0.65, 'f1-score': 0.6666666666666667, 'support': 20.0}, 'NonFlaky': {'precision': 0.8813559322033898, 'recall': 0.896551724137931, 'f1-score': 0.888888888888889, 'support': 58.0}, 'accuracy': 0.8333333333333334, 'macro avg': {'precision': 0.7827832292595897, 'recall': 0.7732758620689655, 'f1-score': 0.7777777777777779, 'support': 78.0}, 'weighted avg': {'precision': 0.8308058281296462, 'recall': 0.8333333333333334, 'f1-score': 0.8319088319088319, 'support': 78.0}}</t>
+    <t>{'Flaky': {'precision': 0.7, 'recall': 0.7, 'f1-score': 0.7, 'support': 20.0}, 'NonFlaky': {'precision': 0.896551724137931, 'recall': 0.896551724137931, 'f1-score': 0.896551724137931, 'support': 58.0}, 'accuracy': 0.8461538461538461, 'macro avg': {'precision': 0.7982758620689655, 'recall': 0.7982758620689655, 'f1-score': 0.7982758620689655, 'support': 78.0}, 'weighted avg': {'precision': 0.8461538461538461, 'recall': 0.8461538461538461, 'f1-score': 0.8461538461538461, 'support': 78.0}}</t>
   </si>
   <si>
     <t>{'Flaky': {'precision': 0.7916666666666666, 'recall': 0.95, 'f1-score': 0.8636363636363635, 'support': 20.0}, 'NonFlaky': {'precision': 0.9814814814814815, 'recall': 0.9137931034482759, 'f1-score': 0.9464285714285714, 'support': 58.0}, 'accuracy': 0.9230769230769231, 'macro avg': {'precision': 0.8865740740740741, 'recall': 0.931896551724138, 'f1-score': 0.9050324675324675, 'support': 78.0}, 'weighted avg': {'precision': 0.9328110161443496, 'recall': 0.9230769230769231, 'f1-score': 0.9251998001998001, 'support': 78.0}}</t>
@@ -389,7 +389,7 @@
     <t>{'Flaky': {'precision': 0.6206896551724138, 'recall': 0.9, 'f1-score': 0.7346938775510204, 'support': 20.0}, 'NonFlaky': {'precision': 0.9672131147540983, 'recall': 0.8428571428571429, 'f1-score': 0.9007633587786259, 'support': 70.0}, 'accuracy': 0.8555555555555555, 'macro avg': {'precision': 0.793951384963256, 'recall': 0.8714285714285714, 'f1-score': 0.8177286181648231, 'support': 90.0}, 'weighted avg': {'precision': 0.8902079015137239, 'recall': 0.8555555555555555, 'f1-score': 0.8638590296169357, 'support': 90.0}}</t>
   </si>
   <si>
-    <t>{'Flaky': {'precision': 0.7, 'recall': 0.7, 'f1-score': 0.7, 'support': 20.0}, 'NonFlaky': {'precision': 0.9142857142857143, 'recall': 0.9142857142857143, 'f1-score': 0.9142857142857143, 'support': 70.0}, 'accuracy': 0.8666666666666667, 'macro avg': {'precision': 0.8071428571428572, 'recall': 0.8071428571428572, 'f1-score': 0.8071428571428572, 'support': 90.0}, 'weighted avg': {'precision': 0.8666666666666667, 'recall': 0.8666666666666667, 'f1-score': 0.8666666666666667, 'support': 90.0}}</t>
+    <t>{'Flaky': {'precision': 0.7777777777777778, 'recall': 0.7, 'f1-score': 0.7368421052631577, 'support': 20.0}, 'NonFlaky': {'precision': 0.9166666666666666, 'recall': 0.9428571428571428, 'f1-score': 0.9295774647887323, 'support': 70.0}, 'accuracy': 0.8888888888888888, 'macro avg': {'precision': 0.8472222222222222, 'recall': 0.8214285714285714, 'f1-score': 0.833209785025945, 'support': 90.0}, 'weighted avg': {'precision': 0.8858024691358024, 'recall': 0.8888888888888888, 'f1-score': 0.8867473848941602, 'support': 90.0}}</t>
   </si>
   <si>
     <t>{'Flaky': {'precision': 1.0, 'recall': 0.65, 'f1-score': 0.787878787878788, 'support': 20.0}, 'NonFlaky': {'precision': 0.9090909090909091, 'recall': 1.0, 'f1-score': 0.9523809523809523, 'support': 70.0}, 'accuracy': 0.9222222222222223, 'macro avg': {'precision': 0.9545454545454546, 'recall': 0.825, 'f1-score': 0.8701298701298701, 'support': 90.0}, 'weighted avg': {'precision': 0.9292929292929292, 'recall': 0.9222222222222223, 'f1-score': 0.9158249158249158, 'support': 90.0}}</t>
@@ -413,7 +413,7 @@
     <t>{'Flaky': {'precision': 0.7904328018223234, 'recall': 0.7986191024165707, 'f1-score': 0.7945048654836864, 'support': 869.0}, 'NonFlaky': {'precision': 0.8390064397424103, 'recall': 0.8321167883211679, 'f1-score': 0.8355474118185983, 'support': 1096.0}, 'accuracy': 0.8173027989821883, 'macro avg': {'precision': 0.8147196207823668, 'recall': 0.8153679453688694, 'f1-score': 0.8150261386511424, 'support': 1965.0}, 'weighted avg': {'precision': 0.8175252736596849, 'recall': 0.8173027989821883, 'f1-score': 0.817396789546314, 'support': 1965.0}}</t>
   </si>
   <si>
-    <t>{'Flaky': {'precision': 0.7988165680473372, 'recall': 0.7767548906789413, 'f1-score': 0.7876312718786465, 'support': 869.0}, 'NonFlaky': {'precision': 0.8267857142857142, 'recall': 0.8448905109489051, 'f1-score': 0.8357400722021661, 'support': 1096.0}, 'accuracy': 0.8147582697201018, 'macro avg': {'precision': 0.8128011411665257, 'recall': 0.8108227008139233, 'f1-score': 0.8116856720404062, 'support': 1965.0}, 'weighted avg': {'precision': 0.814416661827114, 'recall': 0.8147582697201018, 'f1-score': 0.8144644755196528, 'support': 1965.0}}</t>
+    <t>{'Flaky': {'precision': 0.7669345579793341, 'recall': 0.7686996547756041, 'f1-score': 0.767816091954023, 'support': 869.0}, 'NonFlaky': {'precision': 0.8162705667276051, 'recall': 0.8147810218978102, 'f1-score': 0.8155251141552511, 'support': 1096.0}, 'accuracy': 0.7944020356234097, 'macro avg': {'precision': 0.7916025623534696, 'recall': 0.7917403383367072, 'f1-score': 0.791670603054637, 'support': 1965.0}, 'weighted avg': {'precision': 0.7944522503905834, 'recall': 0.7944020356234097, 'f1-score': 0.794426315024021, 'support': 1965.0}}</t>
   </si>
   <si>
     <t>{'Flaky': {'precision': 0.6914778856526429, 'recall': 0.7376294591484465, 'f1-score': 0.7138084632516705, 'support': 869.0}, 'NonFlaky': {'precision': 0.7803468208092486, 'recall': 0.7390510948905109, 'f1-score': 0.7591377694470477, 'support': 1096.0}, 'accuracy': 0.7384223918575064, 'macro avg': {'precision': 0.7359123532309457, 'recall': 0.7383402770194787, 'f1-score': 0.7364731163493591, 'support': 1965.0}, 'weighted avg': {'precision': 0.7410454952870652, 'recall': 0.7384223918575064, 'f1-score': 0.7390913739845628, 'support': 1965.0}}</t>
@@ -437,7 +437,7 @@
     <t>{'Flaky': {'precision': 0.7184801381692574, 'recall': 0.8455284552845529, 'f1-score': 0.776844070961718, 'support': 984.0}, 'NonFlaky': {'precision': 0.8529980657640233, 'recall': 0.7301324503311258, 'f1-score': 0.7867975022301517, 'support': 1208.0}, 'accuracy': 0.781934306569343, 'macro avg': {'precision': 0.7857391019666403, 'recall': 0.7878304528078394, 'f1-score': 0.7818207865959348, 'support': 2192.0}, 'weighted avg': {'precision': 0.7926122807488546, 'recall': 0.781934306569343, 'f1-score': 0.7823293560768038, 'support': 2192.0}}</t>
   </si>
   <si>
-    <t>{'Flaky': {'precision': 0.6993583868011, 'recall': 0.7754065040650406, 'f1-score': 0.7354216867469879, 'support': 984.0}, 'NonFlaky': {'precision': 0.7992733878292462, 'recall': 0.7284768211920529, 'f1-score': 0.7622347336509311, 'support': 1208.0}, 'accuracy': 0.7495437956204379, 'macro avg': {'precision': 0.7493158873151731, 'recall': 0.7519416626285468, 'f1-score': 0.7488282101989595, 'support': 2192.0}, 'weighted avg': {'precision': 0.7544210333531075, 'recall': 0.7495437956204379, 'f1-score': 0.7501982198947814, 'support': 2192.0}}</t>
+    <t>{'Flaky': {'precision': 0.6704745166959578, 'recall': 0.7754065040650406, 'f1-score': 0.7191328934967013, 'support': 984.0}, 'NonFlaky': {'precision': 0.7903225806451613, 'recall': 0.6895695364238411, 'f1-score': 0.7365163572060124, 'support': 1208.0}, 'accuracy': 0.7281021897810219, 'macro avg': {'precision': 0.7303985486705595, 'recall': 0.7324880202444408, 'f1-score': 0.7278246253513568, 'support': 2192.0}, 'weighted avg': {'precision': 0.7365221723759933, 'recall': 0.7281021897810219, 'f1-score': 0.7287128315262851, 'support': 2192.0}}</t>
   </si>
   <si>
     <t>{'Flaky': {'precision': 0.6745762711864407, 'recall': 0.8089430894308943, 'f1-score': 0.7356746765249539, 'support': 984.0}, 'NonFlaky': {'precision': 0.8142292490118577, 'recall': 0.6821192052980133, 'f1-score': 0.7423423423423424, 'support': 1208.0}, 'accuracy': 0.7390510948905109, 'macro avg': {'precision': 0.7444027600991492, 'recall': 0.7455311473644538, 'f1-score': 0.7390085094336482, 'support': 2192.0}, 'weighted avg': {'precision': 0.7515383137106668, 'recall': 0.7390510948905109, 'f1-score': 0.7393491930885513, 'support': 2192.0}}</t>
@@ -461,7 +461,7 @@
     <t>{'Flaky': {'precision': 0.5708812260536399, 'recall': 0.861271676300578, 'f1-score': 0.6866359447004609, 'support': 173.0}, 'NonFlaky': {'precision': 0.8666666666666667, 'recall': 0.582089552238806, 'f1-score': 0.6964285714285713, 'support': 268.0}, 'accuracy': 0.691609977324263, 'macro avg': {'precision': 0.7187739463601532, 'recall': 0.721680614269692, 'f1-score': 0.691532258064516, 'support': 441.0}, 'weighted avg': {'precision': 0.7506329223899011, 'recall': 0.691609977324263, 'f1-score': 0.6925870194467956, 'support': 441.0}}</t>
   </si>
   <si>
-    <t>{'Flaky': {'precision': 0.5952380952380952, 'recall': 0.7225433526011561, 'f1-score': 0.6527415143603134, 'support': 173.0}, 'NonFlaky': {'precision': 0.7922077922077922, 'recall': 0.6828358208955224, 'f1-score': 0.7334669338677355, 'support': 268.0}, 'accuracy': 0.6984126984126984, 'macro avg': {'precision': 0.6937229437229437, 'recall': 0.7026895867483393, 'f1-score': 0.6931042241140244, 'support': 441.0}, 'weighted avg': {'precision': 0.7149385006527864, 'recall': 0.6984126984126984, 'f1-score': 0.7017991389135767, 'support': 441.0}}</t>
+    <t>{'Flaky': {'precision': 0.5794392523364486, 'recall': 0.7167630057803468, 'f1-score': 0.6408268733850129, 'support': 173.0}, 'NonFlaky': {'precision': 0.7841409691629956, 'recall': 0.664179104477612, 'f1-score': 0.719191919191919, 'support': 268.0}, 'accuracy': 0.6848072562358276, 'macro avg': {'precision': 0.6817901107497221, 'recall': 0.6904710551289794, 'f1-score': 0.6800093962884659, 'support': 441.0}, 'weighted avg': {'precision': 0.7038384816097243, 'recall': 0.6848072562358276, 'f1-score': 0.688450075825491, 'support': 441.0}}</t>
   </si>
   <si>
     <t>{'Flaky': {'precision': 0.6050955414012739, 'recall': 0.5491329479768786, 'f1-score': 0.5757575757575757, 'support': 173.0}, 'NonFlaky': {'precision': 0.7253521126760564, 'recall': 0.7686567164179104, 'f1-score': 0.7463768115942029, 'support': 268.0}, 'accuracy': 0.6825396825396826, 'macro avg': {'precision': 0.6652238270386651, 'recall': 0.6588948321973945, 'f1-score': 0.6610671936758893, 'support': 441.0}, 'weighted avg': {'precision': 0.6781766323347017, 'recall': 0.6825396825396826, 'f1-score': 0.6794445490097665, 'support': 441.0}}</t>
@@ -485,7 +485,7 @@
     <t>{'Flaky': {'precision': 0.673202614379085, 'recall': 0.8046875, 'f1-score': 0.7330960854092526, 'support': 1024.0}, 'NonFlaky': {'precision': 0.8215878679750223, 'recall': 0.6971990915972748, 'f1-score': 0.7542997542997542, 'support': 1321.0}, 'accuracy': 0.744136460554371, 'macro avg': {'precision': 0.7473952411770537, 'recall': 0.7509432957986374, 'f1-score': 0.7436979198545034, 'support': 2345.0}, 'weighted avg': {'precision': 0.7567919192832356, 'recall': 0.744136460554371, 'f1-score': 0.7450406681829637, 'support': 2345.0}}</t>
   </si>
   <si>
-    <t>{'Flaky': {'precision': 0.6866725507502206, 'recall': 0.759765625, 'f1-score': 0.7213722763096893, 'support': 1024.0}, 'NonFlaky': {'precision': 0.7970297029702971, 'recall': 0.7312641937925813, 'f1-score': 0.7627319384129491, 'support': 1321.0}, 'accuracy': 0.7437100213219616, 'macro avg': {'precision': 0.7418511268602588, 'recall': 0.7455149093962907, 'f1-score': 0.7420521073613191, 'support': 2345.0}, 'weighted avg': {'precision': 0.7488396288238757, 'recall': 0.7437100213219616, 'f1-score': 0.744671258671483, 'support': 2345.0}}</t>
+    <t>{'Flaky': {'precision': 0.702726473175022, 'recall': 0.7802734375, 'f1-score': 0.7394724664507173, 'support': 1024.0}, 'NonFlaky': {'precision': 0.8137417218543046, 'recall': 0.7441332323996972, 'f1-score': 0.7773823645709766, 'support': 1321.0}, 'accuracy': 0.7599147121535181, 'macro avg': {'precision': 0.7582340975146633, 'recall': 0.7622033349498486, 'f1-score': 0.758427415510847, 'support': 2345.0}, 'weighted avg': {'precision': 0.765264274243394, 'recall': 0.7599147121535181, 'f1-score': 0.7608281062873326, 'support': 2345.0}}</t>
   </si>
   <si>
     <t>{'Flaky': {'precision': 0.6222418358340689, 'recall': 0.6884765625, 'f1-score': 0.6536856745479833, 'support': 1024.0}, 'NonFlaky': {'precision': 0.7367986798679867, 'recall': 0.6760030280090841, 'f1-score': 0.7050927753651797, 'support': 1321.0}, 'accuracy': 0.6814498933901919, 'macro avg': {'precision': 0.6795202578510278, 'recall': 0.682239795254542, 'f1-score': 0.6793892249565815, 'support': 2345.0}, 'weighted avg': {'precision': 0.686774710447632, 'recall': 0.6814498933901919, 'f1-score': 0.6826446426415937, 'support': 2345.0}}</t>
@@ -915,10 +915,10 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>0.8193206136617018</v>
+        <v>0.826096895191876</v>
       </c>
       <c r="D3">
-        <v>0.8101708459630753</v>
+        <v>0.8201074676219344</v>
       </c>
       <c r="E3" t="s">
         <v>15</v>
@@ -927,7 +927,7 @@
         <v>79</v>
       </c>
       <c r="G3">
-        <v>0.634498604225574</v>
+        <v>0.6483610453527003</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1099,10 +1099,10 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>0.7996338672768878</v>
+        <v>0.7903038847117795</v>
       </c>
       <c r="D11">
-        <v>0.8142857142857144</v>
+        <v>0.8190476190476191</v>
       </c>
       <c r="E11" t="s">
         <v>23</v>
@@ -1111,7 +1111,7 @@
         <v>87</v>
       </c>
       <c r="G11">
-        <v>0.5969273626119099</v>
+        <v>0.5779958472674062</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1283,10 +1283,10 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>0.8319088319088319</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="D19">
-        <v>0.8464285714285713</v>
+        <v>0.8339285714285714</v>
       </c>
       <c r="E19" t="s">
         <v>31</v>
@@ -1295,7 +1295,7 @@
         <v>95</v>
       </c>
       <c r="G19">
-        <v>0.5559778080267602</v>
+        <v>0.596551724137931</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1467,10 +1467,10 @@
         <v>7</v>
       </c>
       <c r="C27">
-        <v>0.8666666666666667</v>
+        <v>0.8867473848941602</v>
       </c>
       <c r="D27">
-        <v>0.9111111111111111</v>
+        <v>0.888888888888889</v>
       </c>
       <c r="E27" t="s">
         <v>39</v>
@@ -1479,7 +1479,7 @@
         <v>103</v>
       </c>
       <c r="G27">
-        <v>0.6142857142857143</v>
+        <v>0.668153104781061</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1651,10 +1651,10 @@
         <v>7</v>
       </c>
       <c r="C35">
-        <v>0.8144644755196528</v>
+        <v>0.7944263150240209</v>
       </c>
       <c r="D35">
-        <v>0.810393142028385</v>
+        <v>0.8103724230809075</v>
       </c>
       <c r="E35" t="s">
         <v>47</v>
@@ -1663,7 +1663,7 @@
         <v>111</v>
       </c>
       <c r="G35">
-        <v>0.6236207036815143</v>
+        <v>0.5833428844199677</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1835,10 +1835,10 @@
         <v>7</v>
       </c>
       <c r="C43">
-        <v>0.7501982198947814</v>
+        <v>0.7287128315262851</v>
       </c>
       <c r="D43">
-        <v>0.7484101286841012</v>
+        <v>0.7347903694479038</v>
       </c>
       <c r="E43" t="s">
         <v>55</v>
@@ -1847,7 +1847,7 @@
         <v>119</v>
       </c>
       <c r="G43">
-        <v>0.5012506724978875</v>
+        <v>0.4628818529500194</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -2019,10 +2019,10 @@
         <v>7</v>
       </c>
       <c r="C51">
-        <v>0.7017991389135767</v>
+        <v>0.688450075825491</v>
       </c>
       <c r="D51">
-        <v>0.6762121212121214</v>
+        <v>0.6898989898989899</v>
       </c>
       <c r="E51" t="s">
         <v>63</v>
@@ -2031,7 +2031,7 @@
         <v>127</v>
       </c>
       <c r="G51">
-        <v>0.3963111071210356</v>
+        <v>0.3721599344717998</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2203,10 +2203,10 @@
         <v>7</v>
       </c>
       <c r="C59">
-        <v>0.744671258671483</v>
+        <v>0.7608281062873326</v>
       </c>
       <c r="D59">
-        <v>0.7459683578832516</v>
+        <v>0.7425168212402254</v>
       </c>
       <c r="E59" t="s">
         <v>71</v>
@@ -2215,7 +2215,7 @@
         <v>135</v>
       </c>
       <c r="G59">
-        <v>0.487352264787955</v>
+        <v>0.5204222960869725</v>
       </c>
     </row>
     <row r="60" spans="1:7">
